--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487093_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487093_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8175</v>
+        <v>8.730700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9072</v>
+        <v>5.6865</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9103</v>
+        <v>3.0441</v>
       </c>
       <c r="G2" t="n">
         <v>6.4929</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.8398</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8328</v>
+        <v>-0.0535</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7594</v>
+        <v>0.8933</v>
       </c>
       <c r="V2" t="n">
         <v>2.1701</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5875</v>
+        <v>5.4037</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3882</v>
+        <v>2.6059</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1993</v>
+        <v>2.7978</v>
       </c>
       <c r="G3" t="n">
         <v>3.2796</v>
@@ -688,13 +688,13 @@
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8217</v>
+        <v>1.6379</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2295</v>
+        <v>0.4472</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5923</v>
+        <v>1.1907</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2859</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>E. MARTINEZ CENDON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7537</v>
+        <v>4.2701</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1733</v>
+        <v>3.1602</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5804</v>
+        <v>1.1099</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1312</v>
+        <v>0.6242</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2533</v>
+        <v>-0.9274</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1221</v>
+        <v>1.5516</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0643</v>
+        <v>0.798</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7076</v>
+        <v>0.7088</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6433</v>
+        <v>0.0893</v>
       </c>
       <c r="M4" t="n">
-        <v>0.067</v>
+        <v>-0.1739</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4542</v>
+        <v>-1.6361</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5212</v>
+        <v>1.4623</v>
       </c>
       <c r="P4" t="n">
-        <v>0.772</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5646</v>
+        <v>0.2902</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5024</v>
+        <v>-0.2915</v>
       </c>
       <c r="U4" t="n">
-        <v>2.0622</v>
+        <v>0.5816</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2859</v>
+        <v>3.3558</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5717</v>
+        <v>4.5838</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTINEZ CENDON</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5027</v>
+        <v>3.3558</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4999</v>
+        <v>0.632</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0028</v>
+        <v>2.7238</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6242</v>
+        <v>1.1312</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9274</v>
+        <v>1.2533</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5516</v>
+        <v>-0.1221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.798</v>
+        <v>1.0643</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7088</v>
+        <v>1.7076</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0893</v>
+        <v>-0.6433</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1739</v>
+        <v>0.067</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6361</v>
+        <v>-0.4542</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4623</v>
+        <v>0.5212</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4772</v>
+        <v>1.1666</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9518</v>
+        <v>-0.039</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4746</v>
+        <v>1.2056</v>
       </c>
       <c r="V5" t="n">
-        <v>3.3558</v>
+        <v>0.2859</v>
       </c>
       <c r="W5" t="n">
-        <v>4.5838</v>
+        <v>0.5717</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8144</v>
+        <v>2.0609</v>
       </c>
       <c r="E6" t="n">
-        <v>1.274</v>
+        <v>0.7955</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5405</v>
+        <v>1.2654</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8814</v>
+        <v>2.198</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4533</v>
+        <v>1.6932</v>
       </c>
       <c r="I6" t="n">
-        <v>1.428</v>
+        <v>0.5048</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1549</v>
+        <v>2.0173</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3816</v>
+        <v>1.3661</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7733</v>
+        <v>0.6512</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2735</v>
+        <v>0.1807</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9283</v>
+        <v>0.3271</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6546999999999999</v>
+        <v>-0.1464</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>-0.193</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8752</v>
+        <v>0.0559</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7403</v>
+        <v>-0.2568</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1348</v>
+        <v>0.3126</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6336</v>
+        <v>1.5596</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6359</v>
+        <v>0.7514</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9977</v>
+        <v>0.8082</v>
       </c>
       <c r="G7" t="n">
-        <v>2.198</v>
+        <v>1.8814</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6932</v>
+        <v>0.4533</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5048</v>
+        <v>1.428</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0173</v>
+        <v>2.1549</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3661</v>
+        <v>1.3816</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6512</v>
+        <v>0.7733</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1807</v>
+        <v>-0.2735</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3271</v>
+        <v>-0.9283</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1464</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3715</v>
+        <v>0.6203</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4164</v>
+        <v>0.2178</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0449</v>
+        <v>0.4025</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9421</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.216</v>
+        <v>0.7437</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9626</v>
+        <v>-1.3241</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7466</v>
+        <v>2.0678</v>
       </c>
       <c r="G8" t="n">
         <v>3.8655</v>
@@ -1078,13 +1078,13 @@
         <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5724</v>
+        <v>0.3873</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7733</v>
+        <v>-0.1348</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2009</v>
+        <v>0.5221</v>
       </c>
       <c r="V8" t="n">
         <v>-0.614</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9549</v>
+        <v>-0.8964</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6261</v>
+        <v>-1.407</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6712</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3644</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0767</v>
+        <v>-0.0182</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6544</v>
+        <v>-0.4352</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5777</v>
+        <v>0.4171</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3905</v>
+        <v>-0.9691</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5967</v>
+        <v>-2.4966</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2063</v>
+        <v>1.5275</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7009</v>
@@ -1234,13 +1234,13 @@
         <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7667</v>
+        <v>-0.3454</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7139</v>
+        <v>-0.6137</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0529</v>
+        <v>0.2683</v>
       </c>
       <c r="V10" t="n">
         <v>1.2702</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6989</v>
+        <v>-2.22</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6746</v>
+        <v>-3.1957</v>
       </c>
       <c r="F11" t="n">
         <v>0.9757</v>
@@ -1312,10 +1312,10 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2816</v>
+        <v>0.1973</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8923</v>
+        <v>-0.4134</v>
       </c>
       <c r="U11" t="n">
         <v>0.6107</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>20.8491</v>
+        <v>22.039</v>
       </c>
       <c r="E12" t="n">
-        <v>4.018499999999998</v>
+        <v>5.2081</v>
       </c>
       <c r="F12" t="n">
         <v>16.8308</v>
@@ -1390,13 +1390,13 @@
         <v>13.5105</v>
       </c>
       <c r="S12" t="n">
-        <v>3.642</v>
+        <v>4.831700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7627</v>
+        <v>-1.5729</v>
       </c>
       <c r="U12" t="n">
-        <v>6.4046</v>
+        <v>6.404500000000001</v>
       </c>
       <c r="V12" t="n">
         <v>4.9541</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4183</v>
+        <v>2.3356</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4609</v>
+        <v>1.8601</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9574</v>
+        <v>0.4755</v>
       </c>
       <c r="G13" t="n">
         <v>1.1446</v>
@@ -1468,13 +1468,13 @@
         <v>1.7371</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2387</v>
+        <v>0.156</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.033</v>
+        <v>-0.6339</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2717</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.228</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9663</v>
+        <v>0.913</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1436</v>
+        <v>-0.0039</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1773</v>
+        <v>0.9169</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8546</v>
+        <v>2.3252</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9574</v>
+        <v>4.5736</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1028</v>
+        <v>-2.2484</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9024</v>
+        <v>2.9591</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3247</v>
+        <v>4.9212</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5777</v>
+        <v>-1.9621</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0478</v>
+        <v>-0.6339</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3674</v>
+        <v>-0.3476</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6805</v>
+        <v>-0.2863</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.193</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R14" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3047</v>
+        <v>-0.3976</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2062</v>
+        <v>-0.8602</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0985</v>
+        <v>0.4627</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5295</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.7575</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.799</v>
+        <v>0.7462</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0963</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7027</v>
+        <v>-0.097</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3252</v>
+        <v>0.8546</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5736</v>
+        <v>0.9574</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.2484</v>
+        <v>-0.1028</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9591</v>
+        <v>1.9024</v>
       </c>
       <c r="K15" t="n">
-        <v>4.9212</v>
+        <v>1.3247</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.9621</v>
+        <v>0.5777</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6339</v>
+        <v>-1.0478</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3476</v>
+        <v>-0.3674</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2863</v>
+        <v>-0.6805</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5441</v>
+        <v>-0.193</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5116000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7601</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2485</v>
+        <v>0.1788</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5295</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7575</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1006</v>
+        <v>-0.0005</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4326</v>
+        <v>-0.3325</v>
       </c>
       <c r="F16" t="n">
         <v>0.332</v>
@@ -1702,10 +1702,10 @@
         <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4455</v>
+        <v>-0.3454</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4759</v>
+        <v>-0.3758</v>
       </c>
       <c r="U16" t="n">
         <v>0.0304</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8176</v>
+        <v>-0.196</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0091</v>
+        <v>-1.7086</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1914</v>
+        <v>1.5127</v>
       </c>
       <c r="G17" t="n">
         <v>-1.283</v>
@@ -1780,13 +1780,13 @@
         <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6927</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8328</v>
+        <v>-0.5324</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1401</v>
+        <v>0.4614</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8124</v>
+        <v>-2.6656</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.742</v>
+        <v>-3.5417</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9296</v>
+        <v>0.876</v>
       </c>
       <c r="G19" t="n">
         <v>-2.8957</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8818</v>
+        <v>-0.735</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2492</v>
+        <v>-1.049</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3675</v>
+        <v>0.3139</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.6103</v>
+        <v>-4.6791</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7907</v>
+        <v>-2.1349</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8196</v>
+        <v>-2.5442</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9056</v>
+        <v>-2.6599</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1323</v>
+        <v>-1.2533</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7733</v>
+        <v>-1.4066</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2583</v>
+        <v>-0.5707</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6314</v>
+        <v>0.0155</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6269</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6473</v>
+        <v>-2.0892</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5009</v>
+        <v>-1.2688</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1464</v>
+        <v>-0.8204</v>
       </c>
       <c r="P20" t="n">
         <v>-0.193</v>
@@ -2014,28 +2014,28 @@
         <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2723</v>
+        <v>-0.5982</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1468</v>
+        <v>-0.5992</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1256</v>
+        <v>0.001</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.784</v>
+        <v>-1.228</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0699</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.806</v>
+        <v>-4.6859</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2351</v>
+        <v>-2.1142</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5709</v>
+        <v>-2.5716</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6599</v>
+        <v>-3.0798</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2533</v>
+        <v>-0.535</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4066</v>
+        <v>-2.5448</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5707</v>
+        <v>0.1173</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0155</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0892</v>
+        <v>-3.1971</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2688</v>
+        <v>-1.2956</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8204</v>
+        <v>-1.9014</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7251</v>
+        <v>-1.0923</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6993</v>
+        <v>-0.9154</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0258</v>
+        <v>-0.1768</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.228</v>
+        <v>-0.8999</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>G. MARTINEZ DE OSABA ANTOLIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9665</v>
+        <v>-4.8572</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3145</v>
+        <v>-2.0912</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.652</v>
+        <v>-2.766</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0798</v>
+        <v>-1.9056</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.535</v>
+        <v>-1.1323</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5448</v>
+        <v>-0.7733</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1173</v>
+        <v>-1.2583</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7606000000000001</v>
+        <v>-0.6314</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6433</v>
+        <v>-0.6269</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1971</v>
+        <v>-0.6473</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2956</v>
+        <v>-0.5009</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9014</v>
+        <v>-0.1464</v>
       </c>
       <c r="P22" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3729</v>
+        <v>0.0255</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1157</v>
+        <v>-0.1537</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2571</v>
+        <v>0.1791</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8999</v>
+        <v>-2.784</v>
       </c>
       <c r="W22" t="n">
-        <v>0.614</v>
+        <v>0.2859</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5138</v>
+        <v>-3.0699</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0657</v>
+        <v>-5.9061</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.147</v>
+        <v>-4.7464</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9188</v>
+        <v>-1.1597</v>
       </c>
       <c r="G23" t="n">
         <v>-5.102</v>
@@ -2248,13 +2248,13 @@
         <v>2.7021</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5308</v>
+        <v>-0.3711</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2942</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7634</v>
+        <v>0.5225</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1701</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-20.8491</v>
+        <v>-20.8492</v>
       </c>
       <c r="E24" t="n">
-        <v>-15.6028</v>
+        <v>-15.6027</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.2465</v>
+        <v>-5.2464</v>
       </c>
       <c r="G24" t="n">
         <v>-14.1833</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.06709999999999913</v>
+        <v>-0.06710000000000058</v>
       </c>
       <c r="I24" t="n">
         <v>-14.1162</v>
@@ -2302,16 +2302,16 @@
         <v>-1.002</v>
       </c>
       <c r="K24" t="n">
-        <v>6.245</v>
+        <v>6.244999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-7.247000000000001</v>
+        <v>-7.247</v>
       </c>
       <c r="M24" t="n">
         <v>-13.181</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.312200000000001</v>
+        <v>-6.3122</v>
       </c>
       <c r="O24" t="n">
         <v>-6.8689</v>
@@ -2326,10 +2326,10 @@
         <v>15.4405</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.642100000000001</v>
+        <v>-3.6419</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.4046</v>
+        <v>-6.4048</v>
       </c>
       <c r="U24" t="n">
         <v>2.7628</v>
